--- a/outputs/master_rename_build/tables/unit_correction_review_queue.xlsx
+++ b/outputs/master_rename_build/tables/unit_correction_review_queue.xlsx
@@ -180,7 +180,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="1">
-        <v>4451</v>
+        <v>4445</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1">
@@ -211,10 +211,10 @@
       </c>
       <c r="C3" s="1"/>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1">
-        <v>4979</v>
+        <v>4980</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1">
@@ -245,10 +245,10 @@
       </c>
       <c r="C4" s="1"/>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="1">
-        <v>4980</v>
+        <v>4975</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1">
@@ -279,10 +279,10 @@
       </c>
       <c r="C5" s="1"/>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1">
-        <v>4982</v>
+        <v>4978</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1">
@@ -313,10 +313,10 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" s="1">
-        <v>4985</v>
+        <v>4981</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1">

--- a/outputs/master_rename_build/tables/unit_correction_review_queue.xlsx
+++ b/outputs/master_rename_build/tables/unit_correction_review_queue.xlsx
@@ -180,7 +180,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="1">
-        <v>4445</v>
+        <v>4449</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1">
@@ -214,7 +214,7 @@
         <v>9</v>
       </c>
       <c r="E3" s="1">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1">
@@ -282,7 +282,7 @@
         <v>9</v>
       </c>
       <c r="E5" s="1">
-        <v>4978</v>
+        <v>4979</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1">
@@ -316,7 +316,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="1">
-        <v>4981</v>
+        <v>4980</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1">

--- a/outputs/master_rename_build/tables/unit_correction_review_queue.xlsx
+++ b/outputs/master_rename_build/tables/unit_correction_review_queue.xlsx
@@ -13,11 +13,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="34" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="38" uniqueCount="25">
   <si>
     <t>pull_item</t>
   </si>
   <si>
+    <t>mineral or spring water, all drinking water sold in containers</t>
+  </si>
+  <si>
     <t>fresh fish</t>
   </si>
   <si>
@@ -27,6 +30,9 @@
     <t>harmonized_nsu_unit</t>
   </si>
   <si>
+    <t>distilled water</t>
+  </si>
+  <si>
     <t>pieces or units</t>
   </si>
   <si>
@@ -39,6 +45,9 @@
     <t>unit</t>
   </si>
   <si>
+    <t>Litres (L)</t>
+  </si>
+  <si>
     <t>grams (g)</t>
   </si>
   <si>
@@ -73,6 +82,9 @@
   </si>
   <si>
     <t>corrected_unit</t>
+  </si>
+  <si>
+    <t>mL</t>
   </si>
   <si>
     <t/>
@@ -121,7 +133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -129,43 +141,43 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2">
@@ -173,18 +185,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1"/>
+        <v>5</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.0070000002160668373</v>
+      </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1">
-        <v>4449</v>
-      </c>
-      <c r="F2" s="1"/>
+        <v>4332</v>
+      </c>
+      <c r="F2" s="1">
+        <v>7.0000002160668373</v>
+      </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
@@ -192,14 +208,20 @@
       <c r="I2" s="1">
         <v>0</v>
       </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
+      <c r="J2" s="1">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1">
+        <v>7.0000002160668373</v>
+      </c>
       <c r="L2" s="1">
         <v>0</v>
       </c>
-      <c r="M2" s="1"/>
+      <c r="M2" s="1">
+        <v>7.0000002160668373</v>
+      </c>
       <c r="N2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -207,14 +229,14 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1">
-        <v>4981</v>
+        <v>4449</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1">
@@ -233,22 +255,22 @@
       </c>
       <c r="M3" s="1"/>
       <c r="N3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E4" s="1">
-        <v>4975</v>
+        <v>4981</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1">
@@ -267,22 +289,22 @@
       </c>
       <c r="M4" s="1"/>
       <c r="N4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E5" s="1">
-        <v>4979</v>
+        <v>4975</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1">
@@ -301,22 +323,22 @@
       </c>
       <c r="M5" s="1"/>
       <c r="N5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1">
-        <v>4980</v>
+        <v>4979</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1">
@@ -335,7 +357,41 @@
       </c>
       <c r="M6" s="1"/>
       <c r="N6" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="1">
+        <v>4980</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1"/>
+      <c r="N7" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/master_rename_build/tables/unit_correction_review_queue.xlsx
+++ b/outputs/master_rename_build/tables/unit_correction_review_queue.xlsx
@@ -236,7 +236,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="1">
-        <v>4449</v>
+        <v>4448</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1">
@@ -270,7 +270,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="1">
-        <v>4981</v>
+        <v>4979</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1">
@@ -304,7 +304,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="1">
-        <v>4975</v>
+        <v>4978</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1">
@@ -335,10 +335,10 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" s="1">
-        <v>4979</v>
+        <v>4980</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1">
@@ -369,10 +369,10 @@
       </c>
       <c r="C7" s="1"/>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" s="1">
-        <v>4980</v>
+        <v>4974</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1">

--- a/outputs/master_rename_build/tables/unit_correction_review_queue.xlsx
+++ b/outputs/master_rename_build/tables/unit_correction_review_queue.xlsx
@@ -236,7 +236,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="1">
-        <v>4448</v>
+        <v>4445</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1">
@@ -267,10 +267,10 @@
       </c>
       <c r="C4" s="1"/>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1">
-        <v>4979</v>
+        <v>4975</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1">
@@ -301,10 +301,10 @@
       </c>
       <c r="C5" s="1"/>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1">
-        <v>4978</v>
+        <v>4979</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1">
@@ -335,7 +335,7 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1">
         <v>4980</v>
@@ -369,10 +369,10 @@
       </c>
       <c r="C7" s="1"/>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" s="1">
-        <v>4974</v>
+        <v>4978</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1">

--- a/outputs/master_rename_build/tables/unit_correction_review_queue.xlsx
+++ b/outputs/master_rename_build/tables/unit_correction_review_queue.xlsx
@@ -270,7 +270,7 @@
         <v>11</v>
       </c>
       <c r="E4" s="1">
-        <v>4975</v>
+        <v>4980</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1">
@@ -304,7 +304,7 @@
         <v>12</v>
       </c>
       <c r="E5" s="1">
-        <v>4979</v>
+        <v>4977</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1">
@@ -335,10 +335,10 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" s="1">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1">
@@ -369,10 +369,10 @@
       </c>
       <c r="C7" s="1"/>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" s="1">
-        <v>4978</v>
+        <v>4975</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1">

--- a/outputs/master_rename_build/tables/unit_correction_review_queue.xlsx
+++ b/outputs/master_rename_build/tables/unit_correction_review_queue.xlsx
@@ -13,14 +13,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="38" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="34" uniqueCount="21">
   <si>
     <t>pull_item</t>
   </si>
   <si>
-    <t>mineral or spring water, all drinking water sold in containers</t>
-  </si>
-  <si>
     <t>fresh fish</t>
   </si>
   <si>
@@ -30,9 +27,6 @@
     <t>harmonized_nsu_unit</t>
   </si>
   <si>
-    <t>distilled water</t>
-  </si>
-  <si>
     <t>pieces or units</t>
   </si>
   <si>
@@ -45,9 +39,6 @@
     <t>unit</t>
   </si>
   <si>
-    <t>Litres (L)</t>
-  </si>
-  <si>
     <t>grams (g)</t>
   </si>
   <si>
@@ -82,9 +73,6 @@
   </si>
   <si>
     <t>corrected_unit</t>
-  </si>
-  <si>
-    <t>mL</t>
   </si>
   <si>
     <t/>
@@ -133,7 +121,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -141,43 +129,43 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>16</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>17</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>18</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>19</v>
-      </c>
-      <c r="L1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2">
@@ -185,22 +173,18 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0.0070000002160668373</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C2" s="1"/>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1">
-        <v>4332</v>
-      </c>
-      <c r="F2" s="1">
-        <v>7.0000002160668373</v>
-      </c>
+        <v>4442</v>
+      </c>
+      <c r="F2" s="1"/>
       <c r="G2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="1">
         <v>0</v>
@@ -208,20 +192,14 @@
       <c r="I2" s="1">
         <v>0</v>
       </c>
-      <c r="J2" s="1">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1">
-        <v>7.0000002160668373</v>
-      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
       <c r="L2" s="1">
         <v>0</v>
       </c>
-      <c r="M2" s="1">
-        <v>7.0000002160668373</v>
-      </c>
+      <c r="M2" s="1"/>
       <c r="N2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -229,14 +207,14 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1">
-        <v>4445</v>
+        <v>4974</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1">
@@ -255,22 +233,22 @@
       </c>
       <c r="M3" s="1"/>
       <c r="N3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E4" s="1">
-        <v>4980</v>
+        <v>4977</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1">
@@ -289,22 +267,22 @@
       </c>
       <c r="M4" s="1"/>
       <c r="N4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E5" s="1">
-        <v>4977</v>
+        <v>4978</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1">
@@ -323,22 +301,22 @@
       </c>
       <c r="M5" s="1"/>
       <c r="N5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E6" s="1">
-        <v>4981</v>
+        <v>4972</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1">
@@ -357,41 +335,7 @@
       </c>
       <c r="M6" s="1"/>
       <c r="N6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="1">
-        <v>4975</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1">
-        <v>0</v>
-      </c>
-      <c r="M7" s="1"/>
-      <c r="N7" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/master_rename_build/tables/unit_correction_review_queue.xlsx
+++ b/outputs/master_rename_build/tables/unit_correction_review_queue.xlsx
@@ -279,10 +279,10 @@
       </c>
       <c r="C5" s="1"/>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1">
-        <v>4978</v>
+        <v>4972</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1">
@@ -313,10 +313,10 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" s="1">
-        <v>4972</v>
+        <v>4978</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1">

--- a/outputs/master_rename_build/tables/unit_correction_review_queue.xlsx
+++ b/outputs/master_rename_build/tables/unit_correction_review_queue.xlsx
@@ -180,7 +180,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="1">
-        <v>4442</v>
+        <v>4462</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1">
@@ -214,7 +214,7 @@
         <v>9</v>
       </c>
       <c r="E3" s="1">
-        <v>4974</v>
+        <v>5001</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1">
@@ -248,7 +248,7 @@
         <v>8</v>
       </c>
       <c r="E4" s="1">
-        <v>4977</v>
+        <v>5004</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1">
@@ -282,7 +282,7 @@
         <v>9</v>
       </c>
       <c r="E5" s="1">
-        <v>4972</v>
+        <v>4999</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1">
@@ -316,7 +316,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="1">
-        <v>4978</v>
+        <v>5005</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1">

--- a/outputs/master_rename_build/tables/unit_correction_review_queue.xlsx
+++ b/outputs/master_rename_build/tables/unit_correction_review_queue.xlsx
@@ -211,10 +211,10 @@
       </c>
       <c r="C3" s="1"/>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" s="1">
-        <v>5001</v>
+        <v>5004</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1">
@@ -245,10 +245,10 @@
       </c>
       <c r="C4" s="1"/>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="1">
-        <v>5004</v>
+        <v>5001</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1">
@@ -279,10 +279,10 @@
       </c>
       <c r="C5" s="1"/>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" s="1">
-        <v>4999</v>
+        <v>5005</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1">
@@ -313,10 +313,10 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" s="1">
-        <v>5005</v>
+        <v>4999</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1">

--- a/outputs/master_rename_build/tables/unit_correction_review_queue.xlsx
+++ b/outputs/master_rename_build/tables/unit_correction_review_queue.xlsx
@@ -211,10 +211,10 @@
       </c>
       <c r="C3" s="1"/>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1">
-        <v>5004</v>
+        <v>5001</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1">
@@ -245,10 +245,10 @@
       </c>
       <c r="C4" s="1"/>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="1">
-        <v>5001</v>
+        <v>5004</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1">
@@ -279,10 +279,10 @@
       </c>
       <c r="C5" s="1"/>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1">
-        <v>5005</v>
+        <v>4999</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1">
@@ -313,10 +313,10 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" s="1">
-        <v>4999</v>
+        <v>5005</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1">

--- a/outputs/master_rename_build/tables/unit_correction_review_queue.xlsx
+++ b/outputs/master_rename_build/tables/unit_correction_review_queue.xlsx
@@ -214,7 +214,7 @@
         <v>9</v>
       </c>
       <c r="E3" s="1">
-        <v>5001</v>
+        <v>4999</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1">
@@ -245,10 +245,10 @@
       </c>
       <c r="C4" s="1"/>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="1">
-        <v>5004</v>
+        <v>5001</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1">
@@ -279,10 +279,10 @@
       </c>
       <c r="C5" s="1"/>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" s="1">
-        <v>4999</v>
+        <v>5004</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1">
